--- a/public/flashcards/minna_lesson_17.xlsx
+++ b/public/flashcards/minna_lesson_17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Chat-Website\public\flashcards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BACA0B-7A84-4124-A967-7D44F1D49581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517C6C65-48DD-4A69-96CC-C8FC3405A590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="114">
   <si>
     <t>Hiragana/Katakana</t>
   </si>
@@ -52,9 +52,6 @@
     <t>oboemasu</t>
   </si>
   <si>
-    <t>จำ, จดจำ</t>
-  </si>
-  <si>
     <t>わすれます</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>wasuremasu</t>
   </si>
   <si>
-    <t>ลืม</t>
-  </si>
-  <si>
     <t>なくします</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>nakushimasu</t>
   </si>
   <si>
-    <t>ทำหาย</t>
-  </si>
-  <si>
     <t>はらいます</t>
   </si>
   <si>
@@ -88,9 +79,6 @@
     <t>haraimasu</t>
   </si>
   <si>
-    <t>จ่าย, ชำระ (เงิน)</t>
-  </si>
-  <si>
     <t>かえします</t>
   </si>
   <si>
@@ -100,9 +88,6 @@
     <t>kaeshimasu</t>
   </si>
   <si>
-    <t>คืน (สิ่งของ)</t>
-  </si>
-  <si>
     <t>でかけます</t>
   </si>
   <si>
@@ -112,9 +97,6 @@
     <t>dekakemasu</t>
   </si>
   <si>
-    <t>ออกไปข้างนอก</t>
-  </si>
-  <si>
     <t>ぬぎます</t>
   </si>
   <si>
@@ -124,9 +106,6 @@
     <t>nugimasu</t>
   </si>
   <si>
-    <t>ถอด (เสื้อผ้า, รองเท้า)</t>
-  </si>
-  <si>
     <t>もっていきます</t>
   </si>
   <si>
@@ -136,9 +115,6 @@
     <t>motte ikimasu</t>
   </si>
   <si>
-    <t>นำไป, ถือไป (สิ่งของ)</t>
-  </si>
-  <si>
     <t>もってきます</t>
   </si>
   <si>
@@ -148,45 +124,24 @@
     <t>motte kimasu</t>
   </si>
   <si>
-    <t>นำมา, ถือมา (สิ่งของ)</t>
-  </si>
-  <si>
     <t>しんぱいします</t>
   </si>
   <si>
     <t>心配します</t>
   </si>
   <si>
-    <t>shinpai-shimasu</t>
-  </si>
-  <si>
-    <t>เป็นห่วง, กังวล</t>
-  </si>
-  <si>
     <t>ざんぎょうします</t>
   </si>
   <si>
     <t>残業します</t>
   </si>
   <si>
-    <t>zangyou-shimasu</t>
-  </si>
-  <si>
-    <t>ทำงานล่วงเวลา (โอที)</t>
-  </si>
-  <si>
     <t>しゅっちょうします</t>
   </si>
   <si>
     <t>出張します</t>
   </si>
   <si>
-    <t>shucchou-shimasu</t>
-  </si>
-  <si>
-    <t>ไปทำงานนอกสถานที่ (ต่างจังหวัด/ต่างประเทศ)</t>
-  </si>
-  <si>
     <t>のみます [くすりを～]</t>
   </si>
   <si>
@@ -196,9 +151,6 @@
     <t>nomimasu [kusuri o ~]</t>
   </si>
   <si>
-    <t>กิน [ยา]</t>
-  </si>
-  <si>
     <t>はいります [おふろに～]</t>
   </si>
   <si>
@@ -208,9 +160,6 @@
     <t>hairimasu [ofuro ni ~]</t>
   </si>
   <si>
-    <t>อาบน้ำ [ในอ่างอาบน้ำ]</t>
-  </si>
-  <si>
     <t>たいせつ [な]</t>
   </si>
   <si>
@@ -220,9 +169,6 @@
     <t>taisetsu [na]</t>
   </si>
   <si>
-    <t>สำคัญ</t>
-  </si>
-  <si>
     <t>だいじょうぶ [な]</t>
   </si>
   <si>
@@ -232,9 +178,6 @@
     <t>daijoubu [na]</t>
   </si>
   <si>
-    <t>ไม่เป็นไร, ไม่มีปัญหา</t>
-  </si>
-  <si>
     <t>あぶない</t>
   </si>
   <si>
@@ -244,9 +187,6 @@
     <t>abunai</t>
   </si>
   <si>
-    <t>อันตราย</t>
-  </si>
-  <si>
     <t>きんえん</t>
   </si>
   <si>
@@ -256,9 +196,6 @@
     <t>kinen</t>
   </si>
   <si>
-    <t>ห้ามสูบบุหรี่</t>
-  </si>
-  <si>
     <t>[けんこう] ほけんしょう</t>
   </si>
   <si>
@@ -268,9 +205,6 @@
     <t>[kenkou] hokenshou</t>
   </si>
   <si>
-    <t>ใบประกัน [สุขภาพ], บัตรประกันสังคม</t>
-  </si>
-  <si>
     <t>ねつ</t>
   </si>
   <si>
@@ -280,9 +214,6 @@
     <t>netsu</t>
   </si>
   <si>
-    <t>ไข้, ความร้อน</t>
-  </si>
-  <si>
     <t>びょうき</t>
   </si>
   <si>
@@ -292,9 +223,6 @@
     <t>byouki</t>
   </si>
   <si>
-    <t>ไม่สบาย, ป่วย</t>
-  </si>
-  <si>
     <t>くすり</t>
   </si>
   <si>
@@ -304,9 +232,6 @@
     <t>kusuri</t>
   </si>
   <si>
-    <t>ยา</t>
-  </si>
-  <si>
     <t>[お] ふろ</t>
   </si>
   <si>
@@ -316,9 +241,6 @@
     <t>[o] furo</t>
   </si>
   <si>
-    <t>อ่างอาบน้ำ</t>
-  </si>
-  <si>
     <t>うわぎ</t>
   </si>
   <si>
@@ -328,9 +250,6 @@
     <t>uwagi</t>
   </si>
   <si>
-    <t>เสื้อตัวนอก, แจ็กเก็ต</t>
-  </si>
-  <si>
     <t>したぎ</t>
   </si>
   <si>
@@ -340,9 +259,6 @@
     <t>shitagi</t>
   </si>
   <si>
-    <t>ชุดชั้นใน</t>
-  </si>
-  <si>
     <t>2、3にち</t>
   </si>
   <si>
@@ -352,27 +268,15 @@
     <t>2, 3 nichi</t>
   </si>
   <si>
-    <t>สองสามวัน</t>
-  </si>
-  <si>
-    <t>2、3～</t>
-  </si>
-  <si>
     <t>2, 3 ~</t>
   </si>
   <si>
-    <t>สองสาม～ (จำนวน)</t>
-  </si>
-  <si>
     <t>どうしましたか。</t>
   </si>
   <si>
     <t>Dou shimashita ka.</t>
   </si>
   <si>
-    <t>เป็นอะไรไปครับ/คะ (หมอถามคนไข้), เกิดอะไรขึ้น</t>
-  </si>
-  <si>
     <t>のど</t>
   </si>
   <si>
@@ -385,18 +289,6 @@
     <t>คอ, ลำคอ</t>
   </si>
   <si>
-    <t>いたい</t>
-  </si>
-  <si>
-    <t>痛い</t>
-  </si>
-  <si>
-    <t>itai</t>
-  </si>
-  <si>
-    <t>เจ็บ, ปวด</t>
-  </si>
-  <si>
     <t>かぜ</t>
   </si>
   <si>
@@ -406,18 +298,12 @@
     <t>kaze</t>
   </si>
   <si>
-    <t>หวัด</t>
-  </si>
-  <si>
     <t>それから</t>
   </si>
   <si>
     <t>sorekara</t>
   </si>
   <si>
-    <t>แล้วก็..., และ... (ใช้เชื่อมประโยค)</t>
-  </si>
-  <si>
     <t>おだいじに。</t>
   </si>
   <si>
@@ -427,32 +313,71 @@
     <t>Odaiji ni.</t>
   </si>
   <si>
-    <t>ขอให้หายเร็วๆ นะครับ/คะ (ใช้พูดกับผู้ป่วย)</t>
-  </si>
-  <si>
     <t>～までに</t>
   </si>
   <si>
     <t>~ made ni</t>
   </si>
   <si>
-    <t>ภายใน～, ก่อน～ (กำหนดเวลา)</t>
-  </si>
-  <si>
     <t>ですから</t>
   </si>
   <si>
     <t>desukara</t>
   </si>
   <si>
-    <t>เพราะฉะนั้น, ดังนั้น (ใช้เชื่อมประโยค)</t>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>shinpaishimasu</t>
+  </si>
+  <si>
+    <t>zangyoushimasu</t>
+  </si>
+  <si>
+    <t>shucchoushimasu</t>
+  </si>
+  <si>
+    <t>2、3</t>
+  </si>
+  <si>
+    <t>[～が] いたいです。</t>
+  </si>
+  <si>
+    <t>[～が] 痛いです。</t>
+  </si>
+  <si>
+    <t>[~ ga] itai desu.</t>
+  </si>
+  <si>
+    <t>เป็นอะไรหรือครับ/คะ, เกิดอะไรขึ้น</t>
+  </si>
+  <si>
+    <t>เจ็บ [~], ปวด [~]</t>
+  </si>
+  <si>
+    <t>(เป็น) หวัด</t>
+  </si>
+  <si>
+    <t>แล้วก็, หลังจากนั้น</t>
+  </si>
+  <si>
+    <t>โปรดรักษาสุขภาพด้วย, ขอให้หายป่วยโดยเร็ว (ใช้พูดให้กำลังใจผู้ที่กำลังป่วยอยู่)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,6 +398,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -482,7 +418,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -505,17 +441,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,7 +758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
@@ -806,519 +766,477 @@
     <col min="4" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D8" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A13" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A20" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A24" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A26" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A31" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A35" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="B35" s="4"/>
+      <c r="C35" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A36" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" thickBot="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15.75" thickBot="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="15.75" thickBot="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="15.75" thickBot="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1332,16 +1250,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D910CF-2294-4D9D-A95D-43F979346F87}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
     <col min="3" max="3" width="28.140625" customWidth="1"/>
     <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1352,87 +1271,96 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="47.25" customHeight="1" thickBot="1">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.5" thickBot="1">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="29.25" thickBot="1">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.25" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>132</v>
+        <v>93</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
